--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audre\Documents\Github\Moteur-de-jeu-2D\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF347FC-2844-4521-B77D-D89A7C956BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Feuille1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,106 +25,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
-  <si>
-    <t xml:space="preserve">Matrice de répartition de charges (à remplir à chaque séance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Séance :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX/XX/XXXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tâche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etudiant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charge retenue (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commentaires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attention :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Seules les tâches techniques sont à inscrire (maths, code, ...).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Les tâches autres (gestion, mise en page, ...) seront valorisées à une charge de 0 heure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Les tâches réalisées avec une IA doivent faire apparaître IA dans la colonne Etudiant. Elles ne sont pas prises en compte pour la répartition de la charge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. La colonne 'Charge retenue' contient le temps approximatif. Maximum de 2 heures par étudiant et par séance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. La répartition individuelle est calculée sur la base des heures individuelles retenues et la somme des heures totales retenues.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Cette matrice doit être remplie par le groupe et la répartition indiquée être validée par tout le groupe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Les contributions indiquées doivent refléter l'apport au projet, non le nombre d'heures devant l'écran.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+  <si>
+    <t>Matrice de répartition de charges (à remplir à chaque séance)</t>
+  </si>
+  <si>
+    <t>Séance :</t>
+  </si>
+  <si>
+    <t>XX/XX/XXXX</t>
+  </si>
+  <si>
+    <t>Tâche</t>
+  </si>
+  <si>
+    <t>Etudiant</t>
+  </si>
+  <si>
+    <t>Charge retenue (h)</t>
+  </si>
+  <si>
+    <t>Commentaires</t>
+  </si>
+  <si>
+    <t>Attention :</t>
+  </si>
+  <si>
+    <t>1. Seules les tâches techniques sont à inscrire (maths, code, ...).</t>
+  </si>
+  <si>
+    <t>2. Les tâches autres (gestion, mise en page, ...) seront valorisées à une charge de 0 heure.</t>
+  </si>
+  <si>
+    <t>3. Les tâches réalisées avec une IA doivent faire apparaître IA dans la colonne Etudiant. Elles ne sont pas prises en compte pour la répartition de la charge.</t>
+  </si>
+  <si>
+    <t>4. La colonne 'Charge retenue' contient le temps approximatif. Maximum de 2 heures par étudiant et par séance.</t>
+  </si>
+  <si>
+    <t>5. La répartition individuelle est calculée sur la base des heures individuelles retenues et la somme des heures totales retenues.</t>
+  </si>
+  <si>
+    <t>6. Cette matrice doit être remplie par le groupe et la répartition indiquée être validée par tout le groupe.</t>
+  </si>
+  <si>
+    <t>7. Les contributions indiquées doivent refléter l'apport au projet, non le nombre d'heures devant l'écran.</t>
+  </si>
+  <si>
+    <t>Réponse aux questions du 1.2</t>
+  </si>
+  <si>
+    <t>Audrey</t>
+  </si>
+  <si>
+    <t>20 min</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <u val="single"/>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -132,7 +126,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -140,123 +134,95 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -286,7 +252,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -310,7 +276,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -370,163 +336,169 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="9.14"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="31.88671875" style="7" customWidth="1"/>
+    <col min="6" max="8" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C8" s="9"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="10">
         <v>46274</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audre\Documents\Github\Moteur-de-jeu-2D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF347FC-2844-4521-B77D-D89A7C956BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39AE608-E078-4367-9603-2F642CE6E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Matrice de répartition de charges (à remplir à chaque séance)</t>
   </si>
@@ -79,6 +79,21 @@
   </si>
   <si>
     <t>20 min</t>
+  </si>
+  <si>
+    <t>Configuration du git</t>
+  </si>
+  <si>
+    <t>Mise en place du projet avec SFML</t>
+  </si>
+  <si>
+    <t>Elven</t>
+  </si>
+  <si>
+    <t>10 min</t>
+  </si>
+  <si>
+    <t>1h 30</t>
   </si>
 </sst>
 </file>
@@ -137,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -151,10 +166,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -348,14 +363,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" customWidth="1"/>
+    <col min="5" max="5" width="31.88671875" customWidth="1"/>
     <col min="6" max="8" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -368,7 +383,7 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -376,16 +391,16 @@
       <c r="A4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -403,7 +418,7 @@
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C8" s="9"/>
+      <c r="C8" s="4"/>
       <c r="G8" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -412,39 +427,39 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
+      <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
+      <c r="B15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="7" t="s">
+      <c r="B17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="B18" t="s">
         <v>14</v>
       </c>
     </row>
@@ -452,7 +467,7 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="7">
         <v>46274</v>
       </c>
     </row>
@@ -485,17 +500,47 @@
       </c>
       <c r="E23" s="5"/>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="5"/>
+    </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\audre\Documents\Github\Moteur-de-jeu-2D\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39AE608-E078-4367-9603-2F642CE6E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuille1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -25,110 +20,149 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>Matrice de répartition de charges (à remplir à chaque séance)</t>
-  </si>
-  <si>
-    <t>Séance :</t>
-  </si>
-  <si>
-    <t>XX/XX/XXXX</t>
-  </si>
-  <si>
-    <t>Tâche</t>
-  </si>
-  <si>
-    <t>Etudiant</t>
-  </si>
-  <si>
-    <t>Charge retenue (h)</t>
-  </si>
-  <si>
-    <t>Commentaires</t>
-  </si>
-  <si>
-    <t>Attention :</t>
-  </si>
-  <si>
-    <t>1. Seules les tâches techniques sont à inscrire (maths, code, ...).</t>
-  </si>
-  <si>
-    <t>2. Les tâches autres (gestion, mise en page, ...) seront valorisées à une charge de 0 heure.</t>
-  </si>
-  <si>
-    <t>3. Les tâches réalisées avec une IA doivent faire apparaître IA dans la colonne Etudiant. Elles ne sont pas prises en compte pour la répartition de la charge.</t>
-  </si>
-  <si>
-    <t>4. La colonne 'Charge retenue' contient le temps approximatif. Maximum de 2 heures par étudiant et par séance.</t>
-  </si>
-  <si>
-    <t>5. La répartition individuelle est calculée sur la base des heures individuelles retenues et la somme des heures totales retenues.</t>
-  </si>
-  <si>
-    <t>6. Cette matrice doit être remplie par le groupe et la répartition indiquée être validée par tout le groupe.</t>
-  </si>
-  <si>
-    <t>7. Les contributions indiquées doivent refléter l'apport au projet, non le nombre d'heures devant l'écran.</t>
-  </si>
-  <si>
-    <t>Réponse aux questions du 1.2</t>
-  </si>
-  <si>
-    <t>Audrey</t>
-  </si>
-  <si>
-    <t>20 min</t>
-  </si>
-  <si>
-    <t>Configuration du git</t>
-  </si>
-  <si>
-    <t>Mise en place du projet avec SFML</t>
-  </si>
-  <si>
-    <t>Elven</t>
-  </si>
-  <si>
-    <t>10 min</t>
-  </si>
-  <si>
-    <t>1h 30</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+  <si>
+    <t xml:space="preserve">Matrice de répartition de charges (à remplir à chaque séance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Séance :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX/XX/XXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tâche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etudiant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge retenue (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commentaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attention :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Seules les tâches techniques sont à inscrire (maths, code, ...).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Les tâches autres (gestion, mise en page, ...) seront valorisées à une charge de 0 heure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Les tâches réalisées avec une IA doivent faire apparaître IA dans la colonne Etudiant. Elles ne sont pas prises en compte pour la répartition de la charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. La colonne 'Charge retenue' contient le temps approximatif. Maximum de 2 heures par étudiant et par séance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. La répartition individuelle est calculée sur la base des heures individuelles retenues et la somme des heures totales retenues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Cette matrice doit être remplie par le groupe et la répartition indiquée être validée par tout le groupe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Les contributions indiquées doivent refléter l'apport au projet, non le nombre d'heures devant l'écran.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réponse aux questions du 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuration du git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place du projet avec SFML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alizee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction pour passer de sfml 2 a 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -141,7 +175,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -149,95 +183,135 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+  <cellXfs count="10">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -267,7 +341,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -291,7 +365,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -351,46 +425,47 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" customWidth="1"/>
-    <col min="6" max="8" width="9.109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="31.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="9.11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -404,146 +479,193 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6" t="n">
         <v>46274</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="5" t="s">
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75208333333333299" bottom="0.75208333333333299" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Matrice des tâches.xlsx
+++ b/Matrice des tâches.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
   <si>
     <t xml:space="preserve">Matrice de répartition de charges (à remplir à chaque séance)</t>
   </si>
@@ -100,7 +100,19 @@
     <t xml:space="preserve">Correction pour passer de sfml 2 a 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1h </t>
+    <t xml:space="preserve">30min </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code 1,2 conversion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code 1,2 debug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formule 1,2</t>
   </si>
 </sst>
 </file>
@@ -208,44 +220,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,226 +454,263 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="31.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="31.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="9.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
+      <c r="A4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="G7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="7" t="n">
         <v>46274</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="7" t="n">
         <v>46275</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
+      <c r="A31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="9" t="s">
         <v>26</v>
       </c>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
